--- a/summary/test_data_before_stand_summary.xlsx
+++ b/summary/test_data_before_stand_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,22 +480,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1470</v>
+        <v>7.293697720601438</v>
       </c>
       <c r="C3" t="n">
-        <v>56600</v>
+        <v>10.94378193187972</v>
       </c>
       <c r="D3" t="n">
-        <v>9819.161069225496</v>
+        <v>9.078853544631389</v>
       </c>
       <c r="E3" t="n">
-        <v>9399</v>
+        <v>9.148464968258095</v>
       </c>
       <c r="F3" t="n">
-        <v>4955.51732692645</v>
+        <v>0.5019418094875964</v>
       </c>
       <c r="G3" t="n">
-        <v>24557151.97746827</v>
+        <v>0.2519455801116825</v>
       </c>
     </row>
     <row r="4">
@@ -508,19 +508,19 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1290</v>
+        <v>7.163172390846642</v>
       </c>
       <c r="D4" t="n">
-        <v>99.6737491432488</v>
+        <v>2.038185297532837</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>177.0017915957783</v>
+        <v>2.613299231288824</v>
       </c>
       <c r="G4" t="n">
-        <v>31329.63422811535</v>
+        <v>6.829332872254757</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>4010</v>
+        <v>8.296795865770052</v>
       </c>
       <c r="D5" t="n">
-        <v>438.9026730637423</v>
+        <v>4.220176414687003</v>
       </c>
       <c r="E5" t="n">
-        <v>350</v>
+        <v>5.860786223465865</v>
       </c>
       <c r="F5" t="n">
-        <v>455.2571185812616</v>
+        <v>2.972604951111197</v>
       </c>
       <c r="G5" t="n">
-        <v>207259.0440189129</v>
+        <v>8.836380195370804</v>
       </c>
     </row>
     <row r="6">
@@ -558,19 +558,19 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1526</v>
+        <v>7.331060305218633</v>
       </c>
       <c r="D6" t="n">
-        <v>52.5832762165867</v>
+        <v>0.7065665307167329</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>176.6986705850261</v>
+        <v>1.911742468961815</v>
       </c>
       <c r="G6" t="n">
-        <v>31222.42018651556</v>
+        <v>3.654759267632217</v>
       </c>
     </row>
     <row r="7">
@@ -583,19 +583,19 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>2140</v>
+        <v>7.669028288589683</v>
       </c>
       <c r="D7" t="n">
-        <v>553.9150102810144</v>
+        <v>5.602043154475727</v>
       </c>
       <c r="E7" t="n">
-        <v>460</v>
+        <v>6.133398042996649</v>
       </c>
       <c r="F7" t="n">
-        <v>437.3513241096485</v>
+        <v>1.884928787304872</v>
       </c>
       <c r="G7" t="n">
-        <v>191276.1807004629</v>
+        <v>3.552956533210616</v>
       </c>
     </row>
     <row r="8">
@@ -608,19 +608,19 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>5095</v>
+        <v>8.536211197251999</v>
       </c>
       <c r="D8" t="n">
-        <v>1045.400959561343</v>
+        <v>6.711093538909668</v>
       </c>
       <c r="E8" t="n">
-        <v>988</v>
+        <v>6.896694331622713</v>
       </c>
       <c r="F8" t="n">
-        <v>443.5929763825433</v>
+        <v>1.218197389379283</v>
       </c>
       <c r="G8" t="n">
-        <v>196774.7286959236</v>
+        <v>1.4840048794905</v>
       </c>
     </row>
     <row r="9">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>407</v>
+        <v>6.011267174404161</v>
       </c>
       <c r="C9" t="n">
-        <v>5095</v>
+        <v>8.536211197251999</v>
       </c>
       <c r="D9" t="n">
-        <v>1156.534612748458</v>
+        <v>6.999916872974699</v>
       </c>
       <c r="E9" t="n">
-        <v>1079</v>
+        <v>6.984716320118266</v>
       </c>
       <c r="F9" t="n">
-        <v>398.165819592379</v>
+        <v>0.327841661733267</v>
       </c>
       <c r="G9" t="n">
-        <v>158536.0198916709</v>
+        <v>0.1074801551680298</v>
       </c>
     </row>
     <row r="10">
@@ -658,19 +658,19 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1862</v>
+        <v>7.529943370601589</v>
       </c>
       <c r="D10" t="n">
-        <v>325.9677861549006</v>
+        <v>2.794558794588557</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>420.6102264691034</v>
+        <v>3.261395644273333</v>
       </c>
       <c r="G10" t="n">
-        <v>176912.9626103904</v>
+        <v>10.63670154848507</v>
       </c>
     </row>
     <row r="11">
@@ -683,19 +683,19 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1064</v>
+        <v>6.970730078143525</v>
       </c>
       <c r="D11" t="n">
-        <v>3.543522960932145</v>
+        <v>0.05437128446139285</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>44.04325086437556</v>
+        <v>0.5571793361096506</v>
       </c>
       <c r="G11" t="n">
-        <v>1939.807946702319</v>
+        <v>0.3104488125875911</v>
       </c>
     </row>
     <row r="12">
@@ -705,22 +705,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>407</v>
+        <v>6.011267174404161</v>
       </c>
       <c r="C12" t="n">
-        <v>5095</v>
+        <v>8.536211197251999</v>
       </c>
       <c r="D12" t="n">
-        <v>1486.045921864291</v>
+        <v>7.254488019866098</v>
       </c>
       <c r="E12" t="n">
-        <v>1432</v>
+        <v>7.267525427828172</v>
       </c>
       <c r="F12" t="n">
-        <v>485.5660986532533</v>
+        <v>0.315917454905562</v>
       </c>
       <c r="G12" t="n">
-        <v>235774.4361613409</v>
+        <v>0.0998038383140078</v>
       </c>
     </row>
     <row r="13">
@@ -758,19 +758,19 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1.09861228866811</v>
       </c>
       <c r="D14" t="n">
-        <v>0.06511309115832763</v>
+        <v>0.0447386004169234</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.25230658340628</v>
+        <v>0.1721622194843939</v>
       </c>
       <c r="G14" t="n">
-        <v>0.06365861203015012</v>
+        <v>0.02963982981779263</v>
       </c>
     </row>
     <row r="15">
@@ -858,19 +858,19 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1.09861228866811</v>
       </c>
       <c r="D18" t="n">
-        <v>1.042494859492803</v>
+        <v>0.7099830082212218</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2084716721132496</v>
+        <v>0.08713188168165757</v>
       </c>
       <c r="G18" t="n">
-        <v>0.04346043807369424</v>
+        <v>0.007591964805386374</v>
       </c>
     </row>
     <row r="19">
@@ -880,22 +880,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>1.386294361119891</v>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>2.772588722239781</v>
       </c>
       <c r="D19" t="n">
-        <v>6.385195339273475</v>
+        <v>1.979497979847912</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>1.945910149055313</v>
       </c>
       <c r="F19" t="n">
-        <v>1.508894575192541</v>
+        <v>0.1989979852648218</v>
       </c>
       <c r="G19" t="n">
-        <v>2.276762839045478</v>
+        <v>0.03960019813945823</v>
       </c>
     </row>
     <row r="20">
@@ -908,19 +908,19 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>1.6094379124341</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5812200137080192</v>
+        <v>0.3787168195248</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6474204530720101</v>
+        <v>0.3948438742454708</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4191532430559669</v>
+        <v>0.1559016850291732</v>
       </c>
     </row>
     <row r="21">
@@ -983,19 +983,19 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1424</v>
+        <v>7.261927092702751</v>
       </c>
       <c r="D23" t="n">
-        <v>93.17477724468814</v>
+        <v>2.442117228724737</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>127.744881519076</v>
+        <v>2.589093802101105</v>
       </c>
       <c r="G23" t="n">
-        <v>16318.75475432277</v>
+        <v>6.703406716078356</v>
       </c>
     </row>
     <row r="24">
@@ -1008,19 +1008,19 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>742</v>
+        <v>6.610696044717759</v>
       </c>
       <c r="D24" t="n">
-        <v>48.3139136394791</v>
+        <v>2.357488632341283</v>
       </c>
       <c r="E24" t="n">
-        <v>28</v>
+        <v>3.367295829986474</v>
       </c>
       <c r="F24" t="n">
-        <v>68.88336411315397</v>
+        <v>2.156550928705298</v>
       </c>
       <c r="G24" t="n">
-        <v>4744.917851545349</v>
+        <v>4.650711908099685</v>
       </c>
     </row>
     <row r="25">
@@ -1033,19 +1033,19 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>1012</v>
+        <v>6.920671504248683</v>
       </c>
       <c r="D25" t="n">
-        <v>24.24331734064428</v>
+        <v>0.816892978450839</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>67.22776541956969</v>
+        <v>1.814051628951575</v>
       </c>
       <c r="G25" t="n">
-        <v>4519.572443308691</v>
+        <v>3.290783312501864</v>
       </c>
     </row>
     <row r="26">
@@ -1058,19 +1058,19 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>360</v>
+        <v>5.888877958332881</v>
       </c>
       <c r="D26" t="n">
-        <v>1.794379712131597</v>
+        <v>0.0467024546119429</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>20.2078417514965</v>
+        <v>0.4939944844890063</v>
       </c>
       <c r="G26" t="n">
-        <v>408.356868253525</v>
+        <v>0.2440305507055591</v>
       </c>
     </row>
     <row r="27">
@@ -1083,19 +1083,19 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>576</v>
+        <v>6.3578422665081</v>
       </c>
       <c r="D27" t="n">
-        <v>17.06442769019877</v>
+        <v>0.4917840603146576</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>56.60976290691056</v>
+        <v>1.513738240517851</v>
       </c>
       <c r="G27" t="n">
-        <v>3204.665256376627</v>
+        <v>2.291403460806079</v>
       </c>
     </row>
     <row r="28">
@@ -1108,19 +1108,19 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>800</v>
+        <v>6.68586094706836</v>
       </c>
       <c r="D28" t="n">
-        <v>1.744345442083619</v>
+        <v>0.02428834096582839</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>30.49164630534207</v>
+        <v>0.3798284884360747</v>
       </c>
       <c r="G28" t="n">
-        <v>929.7404944100804</v>
+        <v>0.1442696806276333</v>
       </c>
     </row>
     <row r="29">
@@ -1133,19 +1133,19 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>17000</v>
+        <v>9.741027444837728</v>
       </c>
       <c r="D29" t="n">
-        <v>58.16792323509253</v>
+        <v>0.2360782053550468</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>630.8069775897079</v>
+        <v>1.254650252181752</v>
       </c>
       <c r="G29" t="n">
-        <v>397917.4429758623</v>
+        <v>1.574147255299733</v>
       </c>
     </row>
     <row r="30">
@@ -1246,6 +1246,181 @@
       </c>
       <c r="G33" t="n">
         <v>1.694527416508479</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TotalArea</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>6.418364935936212</v>
+      </c>
+      <c r="C34" t="n">
+        <v>9.229260256828693</v>
+      </c>
+      <c r="D34" t="n">
+        <v>7.789614818999421</v>
+      </c>
+      <c r="E34" t="n">
+        <v>7.796057974316123</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.3124452504956237</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.09762203455727304</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TotalBaths</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>7</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2.226182316655243</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.8318339744062648</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.6919477609765224</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TotalPorchArea</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>7.261927092702751</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4.326485325575935</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5.117993812416755</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.00013555948723</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4.000542256325294</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AvgRoomSize</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4.859812404361672</v>
+      </c>
+      <c r="C37" t="n">
+        <v>6.329720905522696</v>
+      </c>
+      <c r="D37" t="n">
+        <v>5.431099166178482</v>
+      </c>
+      <c r="E37" t="n">
+        <v>5.426417369175352</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.1949484502647431</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.03800489826062503</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LotUtilization</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.03098698696633832</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7146164465643854</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.165294279142186</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.1446729791454053</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.08965021820141213</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.008037161623560806</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Qual_x_Area</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>6.598509028614515</v>
+      </c>
+      <c r="C39" t="n">
+        <v>10.83861966554364</v>
+      </c>
+      <c r="D39" t="n">
+        <v>9.028435957216368</v>
+      </c>
+      <c r="E39" t="n">
+        <v>9.036106025364846</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.5066792737949123</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.2567238864933397</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TotalQualCond</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="n">
+        <v>17</v>
+      </c>
+      <c r="D40" t="n">
+        <v>11.63262508567512</v>
+      </c>
+      <c r="E40" t="n">
+        <v>12</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.731473964317583</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.998002089109646</v>
       </c>
     </row>
   </sheetData>

--- a/summary/test_data_before_stand_summary.xlsx
+++ b/summary/test_data_before_stand_summary.xlsx
@@ -458,19 +458,19 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>152</v>
       </c>
       <c r="D2" t="n">
-        <v>57.91021247429747</v>
+        <v>57.01712328767123</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>63.5</v>
       </c>
       <c r="F2" t="n">
-        <v>32.26605403027446</v>
+        <v>33.72829144694058</v>
       </c>
       <c r="G2" t="n">
-        <v>1041.098242684591</v>
+        <v>1137.597643929765</v>
       </c>
     </row>
     <row r="3">
@@ -480,22 +480,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.293697720601438</v>
+        <v>7.307872780763706</v>
       </c>
       <c r="C3" t="n">
-        <v>10.94378193187972</v>
+        <v>10.95432665973255</v>
       </c>
       <c r="D3" t="n">
-        <v>9.078853544631389</v>
+        <v>9.105028649508421</v>
       </c>
       <c r="E3" t="n">
-        <v>9.148464968258095</v>
+        <v>9.14532156334749</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5019418094875964</v>
+        <v>0.4647630299617741</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2519455801116825</v>
+        <v>0.2160046740192489</v>
       </c>
     </row>
     <row r="4">
@@ -508,19 +508,19 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>7.163172390846642</v>
+        <v>6.634633357861686</v>
       </c>
       <c r="D4" t="n">
-        <v>2.038185297532837</v>
+        <v>1.98481321389611</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2.613299231288824</v>
+        <v>2.55355622536718</v>
       </c>
       <c r="G4" t="n">
-        <v>6.829332872254757</v>
+        <v>6.52064939611148</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8.296795865770052</v>
+        <v>7.691200097522863</v>
       </c>
       <c r="D5" t="n">
-        <v>4.220176414687003</v>
+        <v>4.440234138098999</v>
       </c>
       <c r="E5" t="n">
-        <v>5.860786223465865</v>
+        <v>6.053247687314038</v>
       </c>
       <c r="F5" t="n">
-        <v>2.972604951111197</v>
+        <v>2.908180210628036</v>
       </c>
       <c r="G5" t="n">
-        <v>8.836380195370804</v>
+        <v>8.457512137488528</v>
       </c>
     </row>
     <row r="6">
@@ -558,19 +558,19 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>7.331060305218633</v>
+        <v>7.02197642307216</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7065665307167329</v>
+        <v>0.7252585856118822</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.911742468961815</v>
+        <v>1.930124073435294</v>
       </c>
       <c r="G6" t="n">
-        <v>3.654759267632217</v>
+        <v>3.725378938854454</v>
       </c>
     </row>
     <row r="7">
@@ -583,19 +583,19 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>7.669028288589683</v>
+        <v>7.622174594817622</v>
       </c>
       <c r="D7" t="n">
-        <v>5.602043154475727</v>
+        <v>5.588496596015319</v>
       </c>
       <c r="E7" t="n">
-        <v>6.133398042996649</v>
+        <v>6.07073772800249</v>
       </c>
       <c r="F7" t="n">
-        <v>1.884928787304872</v>
+        <v>1.869654195656036</v>
       </c>
       <c r="G7" t="n">
-        <v>3.552956533210616</v>
+        <v>3.495606811334218</v>
       </c>
     </row>
     <row r="8">
@@ -608,19 +608,19 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>8.536211197251999</v>
+        <v>3206</v>
       </c>
       <c r="D8" t="n">
-        <v>6.711093538909668</v>
+        <v>1049.256849315068</v>
       </c>
       <c r="E8" t="n">
-        <v>6.896694331622713</v>
+        <v>999</v>
       </c>
       <c r="F8" t="n">
-        <v>1.218197389379283</v>
+        <v>415.9404767433382</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4840048794905</v>
+        <v>173006.4801934755</v>
       </c>
     </row>
     <row r="9">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.011267174404161</v>
+        <v>372</v>
       </c>
       <c r="C9" t="n">
-        <v>8.536211197251999</v>
+        <v>2364</v>
       </c>
       <c r="D9" t="n">
-        <v>6.999916872974699</v>
+        <v>1160.61301369863</v>
       </c>
       <c r="E9" t="n">
-        <v>6.984716320118266</v>
+        <v>1078</v>
       </c>
       <c r="F9" t="n">
-        <v>0.327841661733267</v>
+        <v>365.8347948865025</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1074801551680298</v>
+        <v>133835.0971496493</v>
       </c>
     </row>
     <row r="10">
@@ -658,19 +658,19 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>7.529943370601589</v>
+        <v>7.371489295214277</v>
       </c>
       <c r="D10" t="n">
-        <v>2.794558794588557</v>
+        <v>2.665547087412047</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>3.261395644273333</v>
+        <v>3.250677121688259</v>
       </c>
       <c r="G10" t="n">
-        <v>10.63670154848507</v>
+        <v>10.56690174946747</v>
       </c>
     </row>
     <row r="11">
@@ -683,19 +683,19 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>6.970730078143525</v>
+        <v>6.242223265455165</v>
       </c>
       <c r="D11" t="n">
-        <v>0.05437128446139285</v>
+        <v>0.1144552930558493</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5571793361096506</v>
+        <v>0.7953570825864454</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3104488125875911</v>
+        <v>0.6325928888204218</v>
       </c>
     </row>
     <row r="12">
@@ -705,22 +705,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.011267174404161</v>
+        <v>6.447305862541213</v>
       </c>
       <c r="C12" t="n">
-        <v>8.536211197251999</v>
+        <v>8.09559870137819</v>
       </c>
       <c r="D12" t="n">
-        <v>7.254488019866098</v>
+        <v>7.250879417027849</v>
       </c>
       <c r="E12" t="n">
-        <v>7.267525427828172</v>
+        <v>7.280345604456958</v>
       </c>
       <c r="F12" t="n">
-        <v>0.315917454905562</v>
+        <v>0.3178007769689655</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0998038383140078</v>
+        <v>0.1009973338420781</v>
       </c>
     </row>
     <row r="13">
@@ -733,19 +733,19 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4338588074023303</v>
+        <v>0.4794520547945205</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5305271952308472</v>
+        <v>0.513985546512015</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2814591048795095</v>
+        <v>0.2641811420232547</v>
       </c>
     </row>
     <row r="14">
@@ -758,19 +758,19 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1.09861228866811</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0447386004169234</v>
+        <v>0.02611170885671027</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1721622194843939</v>
+        <v>0.1322017010718455</v>
       </c>
       <c r="G14" t="n">
-        <v>0.02963982981779263</v>
+        <v>0.0174772897662896</v>
       </c>
     </row>
     <row r="15">
@@ -783,19 +783,19 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>1.570938999314599</v>
+        <v>1.527397260273973</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5551898880356613</v>
+        <v>0.5268750574643244</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3082358117770501</v>
+        <v>0.2775973261780351</v>
       </c>
     </row>
     <row r="16">
@@ -808,19 +808,19 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1.09861228866811</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3776559287183002</v>
+        <v>0.2439187005509554</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5030166769415858</v>
+        <v>0.3384435425399239</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2530257772813557</v>
+        <v>0.1145440314869733</v>
       </c>
     </row>
     <row r="17">
@@ -836,16 +836,16 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>2.854009595613434</v>
+        <v>2.832191780821918</v>
       </c>
       <c r="E17" t="n">
         <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8297883627354511</v>
+        <v>0.8054312994998394</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6885487269311806</v>
+        <v>0.6487195782139999</v>
       </c>
     </row>
     <row r="18">
@@ -855,22 +855,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="C18" t="n">
-        <v>1.09861228866811</v>
+        <v>1.386294361119891</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7099830082212218</v>
+        <v>0.7177382384718994</v>
       </c>
       <c r="E18" t="n">
         <v>0.6931471805599453</v>
       </c>
       <c r="F18" t="n">
-        <v>0.08713188168165757</v>
+        <v>0.1004167603936302</v>
       </c>
       <c r="G18" t="n">
-        <v>0.007591964805386374</v>
+        <v>0.01008352576795175</v>
       </c>
     </row>
     <row r="19">
@@ -883,19 +883,19 @@
         <v>1.386294361119891</v>
       </c>
       <c r="C19" t="n">
-        <v>2.772588722239781</v>
+        <v>2.564949357461537</v>
       </c>
       <c r="D19" t="n">
-        <v>1.979497979847912</v>
+        <v>1.984572328802457</v>
       </c>
       <c r="E19" t="n">
         <v>1.945910149055313</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1989979852648218</v>
+        <v>0.2087511119471178</v>
       </c>
       <c r="G19" t="n">
-        <v>0.03960019813945823</v>
+        <v>0.04357702673915811</v>
       </c>
     </row>
     <row r="20">
@@ -908,19 +908,19 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1.6094379124341</v>
+        <v>1.386294361119891</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3787168195248</v>
+        <v>0.382094801834825</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3948438742454708</v>
+        <v>0.4126207778772597</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1559016850291732</v>
+        <v>0.1702559063360349</v>
       </c>
     </row>
     <row r="21">
@@ -933,19 +933,19 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1.764907470870459</v>
+        <v>1.705479452054794</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7770557771054145</v>
+        <v>0.7050900673054168</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6038156807328996</v>
+        <v>0.4971520030127572</v>
       </c>
     </row>
     <row r="22">
@@ -958,19 +958,19 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1488</v>
+        <v>1390</v>
       </c>
       <c r="D22" t="n">
-        <v>472.4448252227553</v>
+        <v>456.9383561643835</v>
       </c>
       <c r="E22" t="n">
         <v>480</v>
       </c>
       <c r="F22" t="n">
-        <v>217.3269021057818</v>
+        <v>200.2585861870057</v>
       </c>
       <c r="G22" t="n">
-        <v>47230.98237889604</v>
+        <v>40103.50134161841</v>
       </c>
     </row>
     <row r="23">
@@ -983,19 +983,19 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>7.261927092702751</v>
+        <v>6.505784060128229</v>
       </c>
       <c r="D23" t="n">
-        <v>2.442117228724737</v>
+        <v>2.540595238750301</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>2.589093802101105</v>
+        <v>2.609038445337779</v>
       </c>
       <c r="G23" t="n">
-        <v>6.703406716078356</v>
+        <v>6.807081609250573</v>
       </c>
     </row>
     <row r="24">
@@ -1008,19 +1008,19 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>6.610696044717759</v>
+        <v>6.261491684321042</v>
       </c>
       <c r="D24" t="n">
-        <v>2.357488632341283</v>
+        <v>2.124834268034769</v>
       </c>
       <c r="E24" t="n">
-        <v>3.367295829986474</v>
+        <v>2.699081350758877</v>
       </c>
       <c r="F24" t="n">
-        <v>2.156550928705298</v>
+        <v>2.152369150473602</v>
       </c>
       <c r="G24" t="n">
-        <v>4.650711908099685</v>
+        <v>4.632692959910455</v>
       </c>
     </row>
     <row r="25">
@@ -1033,19 +1033,19 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>6.920671504248683</v>
+        <v>5.765191102784844</v>
       </c>
       <c r="D25" t="n">
-        <v>0.816892978450839</v>
+        <v>0.7141502448919974</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1.814051628951575</v>
+        <v>1.734361756773039</v>
       </c>
       <c r="G25" t="n">
-        <v>3.290783312501864</v>
+        <v>3.008010703356861</v>
       </c>
     </row>
     <row r="26">
@@ -1058,19 +1058,19 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>5.888877958332881</v>
+        <v>5.771441123130016</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0467024546119429</v>
+        <v>0.09035234404349894</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4939944844890063</v>
+        <v>0.6869282174414908</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2440305507055591</v>
+        <v>0.471870375917344</v>
       </c>
     </row>
     <row r="27">
@@ -1083,19 +1083,19 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>6.3578422665081</v>
+        <v>5.983936280687191</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4917840603146576</v>
+        <v>0.4602403451719119</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1.513738240517851</v>
+        <v>1.478643728768182</v>
       </c>
       <c r="G27" t="n">
-        <v>2.291403460806079</v>
+        <v>2.186387276625472</v>
       </c>
     </row>
     <row r="28">
@@ -1108,19 +1108,19 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>6.68586094706836</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.02428834096582839</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3798284884360747</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1442696806276333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1133,19 +1133,19 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>9.741027444837728</v>
+        <v>8.160803920954665</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2360782053550468</v>
+        <v>0.4379356436209121</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1.254650252181752</v>
+        <v>1.632779351797287</v>
       </c>
       <c r="G29" t="n">
-        <v>1.574147255299733</v>
+        <v>2.665968411655567</v>
       </c>
     </row>
     <row r="30">
@@ -1158,19 +1158,19 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D30" t="n">
-        <v>36.41261137765593</v>
+        <v>40.10616438356164</v>
       </c>
       <c r="E30" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F30" t="n">
-        <v>30.43141570309453</v>
+        <v>30.10426947971987</v>
       </c>
       <c r="G30" t="n">
-        <v>926.0710616945481</v>
+        <v>906.2670409075931</v>
       </c>
     </row>
     <row r="31">
@@ -1186,16 +1186,16 @@
         <v>60</v>
       </c>
       <c r="D31" t="n">
-        <v>24.10897875257025</v>
+        <v>25.27397260273973</v>
       </c>
       <c r="E31" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F31" t="n">
-        <v>21.12945389575932</v>
+        <v>20.60077753443548</v>
       </c>
       <c r="G31" t="n">
-        <v>446.4538219330187</v>
+        <v>424.3920350233017</v>
       </c>
     </row>
     <row r="32">
@@ -1208,19 +1208,19 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D32" t="n">
-        <v>28.57779300891021</v>
+        <v>30.39041095890411</v>
       </c>
       <c r="E32" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F32" t="n">
-        <v>25.95672668397203</v>
+        <v>24.5565126439524</v>
       </c>
       <c r="G32" t="n">
-        <v>673.7516601464257</v>
+        <v>603.0223132325942</v>
       </c>
     </row>
     <row r="33">
@@ -1230,22 +1230,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="C33" t="n">
         <v>2010</v>
       </c>
       <c r="D33" t="n">
-        <v>2007.769705277587</v>
+        <v>2009.599315068493</v>
       </c>
       <c r="E33" t="n">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="F33" t="n">
-        <v>1.301740149380236</v>
+        <v>0.4908785273052907</v>
       </c>
       <c r="G33" t="n">
-        <v>1.694527416508479</v>
+        <v>0.2409617285694111</v>
       </c>
     </row>
     <row r="34">
@@ -1255,22 +1255,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6.418364935936212</v>
+        <v>827</v>
       </c>
       <c r="C34" t="n">
-        <v>9.229260256828693</v>
+        <v>5271</v>
       </c>
       <c r="D34" t="n">
-        <v>7.789614818999421</v>
+        <v>2530.071917808219</v>
       </c>
       <c r="E34" t="n">
-        <v>7.796057974316123</v>
+        <v>2439</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3124452504956237</v>
+        <v>734.0528214224325</v>
       </c>
       <c r="G34" t="n">
-        <v>0.09762203455727304</v>
+        <v>538833.5446382337</v>
       </c>
     </row>
     <row r="35">
@@ -1283,19 +1283,19 @@
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="D35" t="n">
-        <v>2.226182316655243</v>
+        <v>2.203767123287671</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8318339744062648</v>
+        <v>0.7646077002442467</v>
       </c>
       <c r="G35" t="n">
-        <v>0.6919477609765224</v>
+        <v>0.5846249352727958</v>
       </c>
     </row>
     <row r="36">
@@ -1308,19 +1308,19 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>7.261927092702751</v>
+        <v>6.620073206530356</v>
       </c>
       <c r="D36" t="n">
-        <v>4.326485325575935</v>
+        <v>4.301194582616764</v>
       </c>
       <c r="E36" t="n">
         <v>5.117993812416755</v>
       </c>
       <c r="F36" t="n">
-        <v>2.00013555948723</v>
+        <v>2.034261192526417</v>
       </c>
       <c r="G36" t="n">
-        <v>4.000542256325294</v>
+        <v>4.138218599419</v>
       </c>
     </row>
     <row r="37">
@@ -1330,22 +1330,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4.859812404361672</v>
+        <v>4.960043507980195</v>
       </c>
       <c r="C37" t="n">
-        <v>6.329720905522696</v>
+        <v>6.057720342885047</v>
       </c>
       <c r="D37" t="n">
-        <v>5.431099166178482</v>
+        <v>5.421950141582177</v>
       </c>
       <c r="E37" t="n">
-        <v>5.426417369175352</v>
+        <v>5.414352730592636</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1949484502647431</v>
+        <v>0.1863067125230541</v>
       </c>
       <c r="G37" t="n">
-        <v>0.03800489826062503</v>
+        <v>0.03471019113114794</v>
       </c>
     </row>
     <row r="38">
@@ -1355,22 +1355,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.03098698696633832</v>
+        <v>0.02906645483806886</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7146164465643854</v>
+        <v>0.5556264658997078</v>
       </c>
       <c r="D38" t="n">
-        <v>0.165294279142186</v>
+        <v>0.1586507872412295</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1446729791454053</v>
+        <v>0.1471405391824757</v>
       </c>
       <c r="F38" t="n">
-        <v>0.08965021820141213</v>
+        <v>0.07878752968243197</v>
       </c>
       <c r="G38" t="n">
-        <v>0.008037161623560806</v>
+        <v>0.006207474833460098</v>
       </c>
     </row>
     <row r="39">
@@ -1380,22 +1380,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>6.598509028614515</v>
+        <v>7.83241092718792</v>
       </c>
       <c r="C39" t="n">
-        <v>10.83861966554364</v>
+        <v>10.17477343917635</v>
       </c>
       <c r="D39" t="n">
-        <v>9.028435957216368</v>
+        <v>9.016527555868853</v>
       </c>
       <c r="E39" t="n">
-        <v>9.036106025364846</v>
+        <v>9.0506958495282</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5066792737949123</v>
+        <v>0.4833366336095773</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2567238864933397</v>
+        <v>0.2336143013890387</v>
       </c>
     </row>
     <row r="40">
@@ -1405,22 +1405,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C40" t="n">
         <v>17</v>
       </c>
       <c r="D40" t="n">
-        <v>11.63262508567512</v>
+        <v>11.61301369863014</v>
       </c>
       <c r="E40" t="n">
         <v>12</v>
       </c>
       <c r="F40" t="n">
-        <v>1.731473964317583</v>
+        <v>1.740235940026372</v>
       </c>
       <c r="G40" t="n">
-        <v>2.998002089109646</v>
+        <v>3.028421126959469</v>
       </c>
     </row>
   </sheetData>

--- a/summary/test_data_before_stand_summary.xlsx
+++ b/summary/test_data_before_stand_summary.xlsx
@@ -608,19 +608,19 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>3206</v>
+        <v>8.073091199693154</v>
       </c>
       <c r="D8" t="n">
-        <v>1049.256849315068</v>
+        <v>6.753677932166965</v>
       </c>
       <c r="E8" t="n">
-        <v>999</v>
+        <v>6.907750778961887</v>
       </c>
       <c r="F8" t="n">
-        <v>415.9404767433382</v>
+        <v>1.116815491813267</v>
       </c>
       <c r="G8" t="n">
-        <v>173006.4801934755</v>
+        <v>1.24727684275411</v>
       </c>
     </row>
     <row r="9">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>372</v>
+        <v>5.921578419643816</v>
       </c>
       <c r="C9" t="n">
-        <v>2364</v>
+        <v>7.768533300926033</v>
       </c>
       <c r="D9" t="n">
-        <v>1160.61301369863</v>
+        <v>7.009130178858684</v>
       </c>
       <c r="E9" t="n">
-        <v>1078</v>
+        <v>6.983789965258135</v>
       </c>
       <c r="F9" t="n">
-        <v>365.8347948865025</v>
+        <v>0.3128406448336303</v>
       </c>
       <c r="G9" t="n">
-        <v>133835.0971496493</v>
+        <v>0.09786926905992165</v>
       </c>
     </row>
     <row r="10">
@@ -808,19 +808,19 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1.09861228866811</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2439187005509554</v>
+        <v>0.3561643835616438</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3384435425399239</v>
+        <v>0.5007173689199395</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1145440314869733</v>
+        <v>0.2507178835381067</v>
       </c>
     </row>
     <row r="17">
@@ -880,22 +880,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.386294361119891</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>2.564949357461537</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>1.984572328802457</v>
+        <v>6.438356164383562</v>
       </c>
       <c r="E19" t="n">
-        <v>1.945910149055313</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2087511119471178</v>
+        <v>1.6138260135221</v>
       </c>
       <c r="G19" t="n">
-        <v>0.04357702673915811</v>
+        <v>2.604434401920633</v>
       </c>
     </row>
     <row r="20">
@@ -908,19 +908,19 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1.386294361119891</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>0.382094801834825</v>
+        <v>0.5993150684931506</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4126207778772597</v>
+        <v>0.6939103376864372</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1702559063360349</v>
+        <v>0.4815115567481053</v>
       </c>
     </row>
     <row r="21">
@@ -1255,22 +1255,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>827</v>
+        <v>6.71901315438526</v>
       </c>
       <c r="C34" t="n">
-        <v>5271</v>
+        <v>8.570165076182343</v>
       </c>
       <c r="D34" t="n">
-        <v>2530.071917808219</v>
+        <v>7.794561060050786</v>
       </c>
       <c r="E34" t="n">
-        <v>2439</v>
+        <v>7.799752562441473</v>
       </c>
       <c r="F34" t="n">
-        <v>734.0528214224325</v>
+        <v>0.2932195072458317</v>
       </c>
       <c r="G34" t="n">
-        <v>538833.5446382337</v>
+        <v>0.08597767942948832</v>
       </c>
     </row>
     <row r="35">
